--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586223</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128586223</v>
+        <v>128805694</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmen, Jmt</t>
+          <t>Markussonsbodarna, Markussonsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486260</v>
+        <v>486242</v>
       </c>
       <c r="R2" t="n">
-        <v>7005661</v>
+        <v>7005612</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +770,788 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128913615</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holmen, Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>486272</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7005681</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128589425</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>486217</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7005726</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Per Sonnvik</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Per Sonnvik</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128913811</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>486267</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7005673</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128589108</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holmen, Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>486305</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7005582</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128589449</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>486217</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7005726</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128586092</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>486260</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7005661</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128589094</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holmen, Holmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>486306</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7005579</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40781-2025 artfynd.xlsx
+++ b/artfynd/A 40781-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128805694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913615</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589425</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913811</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589108</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589449</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586092</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,8 +1592,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>